--- a/data/Penduldata_template.xlsx
+++ b/data/Penduldata_template.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\beego\Desktop\Deployment website\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C375E81-A87D-450F-9732-8E57673EB406}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BADEF3D7-9D46-4881-8E20-DEEA9798FB26}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{7F137006-2375-41E5-A5CE-B1569C4A2868}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="8">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="15">
   <si>
     <t>L_measured</t>
   </si>
@@ -60,14 +60,87 @@
   </si>
   <si>
     <t>Bemærk: Lad være med at skrive andet end selve dataen i dokumentet; ellers er det ikke kompatibelt med hjemmesiden/python.</t>
+  </si>
+  <si>
+    <t>Enheder: [m]</t>
+  </si>
+  <si>
+    <t>[1]</t>
+  </si>
+  <si>
+    <t>[rad]</t>
+  </si>
+  <si>
+    <t>[m^2]</t>
+  </si>
+  <si>
+    <t>[kg]</t>
+  </si>
+  <si>
+    <t>[s]</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">*alpha er andelen af massen som udgøres af snoren: </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">alpha=m_snor/m_total </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve">og </t>
+    </r>
+    <r>
+      <rPr>
+        <i/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>m_total = m_snor+m_lod</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Aptos Narrow"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>.</t>
+    </r>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Aptos Narrow"/>
@@ -445,23 +518,44 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B10C5AA3-6A37-4782-B98D-99DBAF4692C8}">
-  <dimension ref="A1:F20"/>
+  <dimension ref="A1:G20"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="6" width="10.90625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" t="s">
         <v>5</v>
       </c>
-    </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.35">
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A2" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>9</v>
+      </c>
+      <c r="C2" t="s">
+        <v>10</v>
+      </c>
+      <c r="D2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" t="s">
+        <v>12</v>
+      </c>
+      <c r="F2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G2" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>0</v>
       </c>
@@ -481,7 +575,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A4" s="2"/>
       <c r="B4" s="1"/>
       <c r="C4" s="2"/>
@@ -489,7 +583,7 @@
       <c r="E4" s="2"/>
       <c r="F4" s="1"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A5" s="2"/>
       <c r="B5" s="1"/>
       <c r="C5" s="2"/>
@@ -497,7 +591,7 @@
       <c r="E5" s="2"/>
       <c r="F5" s="1"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A6" s="2"/>
       <c r="B6" s="1"/>
       <c r="C6" s="2"/>
@@ -505,7 +599,7 @@
       <c r="E6" s="2"/>
       <c r="F6" s="1"/>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A7" s="2"/>
       <c r="B7" s="1"/>
       <c r="C7" s="2"/>
@@ -513,7 +607,7 @@
       <c r="E7" s="2"/>
       <c r="F7" s="1"/>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A8" s="2"/>
       <c r="B8" s="1"/>
       <c r="C8" s="2"/>
@@ -521,7 +615,7 @@
       <c r="E8" s="2"/>
       <c r="F8" s="1"/>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="2"/>
       <c r="B9" s="1"/>
       <c r="C9" s="2"/>
@@ -529,7 +623,7 @@
       <c r="E9" s="2"/>
       <c r="F9" s="1"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="2"/>
       <c r="B10" s="1"/>
       <c r="C10" s="2"/>
@@ -537,7 +631,7 @@
       <c r="E10" s="2"/>
       <c r="F10" s="1"/>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="2"/>
       <c r="B11" s="1"/>
       <c r="C11" s="2"/>
@@ -545,7 +639,7 @@
       <c r="E11" s="2"/>
       <c r="F11" s="1"/>
     </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="2"/>
       <c r="B12" s="1"/>
       <c r="C12" s="2"/>
@@ -553,7 +647,7 @@
       <c r="E12" s="2"/>
       <c r="F12" s="1"/>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="2"/>
       <c r="B13" s="1"/>
       <c r="C13" s="2"/>
@@ -561,7 +655,7 @@
       <c r="E13" s="2"/>
       <c r="F13" s="1"/>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A14" s="2"/>
       <c r="B14" s="1"/>
       <c r="C14" s="2"/>
@@ -569,7 +663,7 @@
       <c r="E14" s="2"/>
       <c r="F14" s="1"/>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A15" s="2"/>
       <c r="B15" s="1"/>
       <c r="C15" s="2"/>
@@ -577,7 +671,7 @@
       <c r="E15" s="2"/>
       <c r="F15" s="1"/>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A16" s="2"/>
       <c r="B16" s="1"/>
       <c r="C16" s="2"/>
